--- a/output/StructureDefinition-pdex-provider-consent.xlsx
+++ b/output/StructureDefinition-pdex-provider-consent.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2517" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2734" uniqueCount="430">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.1</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T14:48:28-05:00</t>
+    <t>2026-03-17T22:49:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>The PDex Provider Access Consent Profile enables a member to express their preference for the sharing of their healthcare information to providers through the Provider Access API. A member has to actively choose to opt-out of sharing their data.</t>
+    <t>The PDex Provider Access Consent Profile enables a member to express their preference for the sharing of their healthcare information to providers through the Provider Access API. A member has to actively choose to opt-out of sharing their data. The opt-out may be exercised by the patient or by the patient's legally recognized personal representative (e.g., parent, guardian, or healthcare proxy), consistent with CMS-0057-F and HIPAA.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -586,6 +586,9 @@
     <t>Consent.category</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>Classification of the consent statement - for indexing/retrieval</t>
   </si>
   <si>
@@ -631,6 +634,26 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Consent.category:apiPurpose</t>
+  </si>
+  <si>
+    <t>apiPurpose</t>
+  </si>
+  <si>
+    <t>Identifies this Consent as applying to the Provider Access API</t>
+  </si>
+  <si>
+    <t>Fixed to 'provider-access'. Enables systems to locate Provider Access API Consent records for a member using a standard category search (GET /Consent?patient=X&amp;category=provider-access) without relying on actor cross-referencing or custom extension searches.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://hl7.org/fhir/us/davinci-pdex/CodeSystem/pdex-consent-api-purpose"/&gt;
+    &lt;code value="provider-access"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Consent.patient</t>
   </si>
   <si>
@@ -691,7 +714,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
 </t>
   </si>
   <si>
@@ -701,7 +724,7 @@
     <t>Either the Grantor, which is the entity responsible for granting the rights listed in a Consent Directive or the Grantee, which is the entity responsible for complying with the Consent Directive, including any obligations or limitations on authorizations and enforcement of prohibitions.</t>
   </si>
   <si>
-    <t>Commonly, the patient the consent pertains to is the consentor, but particularly for young and old people, it may be some other person - e.g. a legal guardian.</t>
+    <t>The individual who performed the opt-out. This SHALL be either the patient themselves (US Core Patient Profile) or the patient's legally recognized personal representative acting on their behalf (US Core RelatedPerson Profile), such as a parent, guardian, or healthcare proxy, consistent with CMS-0057-F and HIPAA.</t>
   </si>
   <si>
     <t>Event.performer</t>
@@ -1120,42 +1143,98 @@
     <t>Consent.provision.action</t>
   </si>
   <si>
-    <t>Actions controlled by this rule</t>
+    <t>Action permitted or denied - use 'disclose' with provision.type='deny' for Provider Access opt-out</t>
   </si>
   <si>
     <t>Actions controlled by this Rule.</t>
   </si>
   <si>
-    <t>Note that this is the direct action (not the grounds for the action covered in the purpose element). At present, the only action in the understood and tested scope of this resource is 'read'.</t>
+    <t>To opt-out of Provider Access data sharing, set provision.type to 'deny' and provision.action to 'disclose'. The ProviderAccessUseCase extension identifies this consent as specific to the Provider Access API.</t>
   </si>
   <si>
     <t>all actions</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/consentaction"/&gt;
-    &lt;code value="disclose"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Detailed codes for the consent action.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-action|4.0.1</t>
-  </si>
-  <si>
-    <t>Consent.provision.securityLabel</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
+  </si>
+  <si>
+    <t>Consent.provision.action.id</t>
+  </si>
+  <si>
+    <t>Consent.provision.action.extension</t>
+  </si>
+  <si>
+    <t>Consent.provision.action.extension:providerAccessUseCase</t>
+  </si>
+  <si>
+    <t>providerAccessUseCase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/davinci-pdex/StructureDefinition/pdex-provider-access-use-case}
+</t>
+  </si>
+  <si>
+    <t>Indicates this action applies to Provider Access API</t>
+  </si>
+  <si>
+    <t>Indicates that the consent action is specifically related to the Provider Access API use case for sharing or withholding member data with providers.</t>
+  </si>
+  <si>
+    <t>Consent.provision.action.coding</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
 </t>
   </si>
   <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Consent.provision.action.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>Consent.provision.securityLabel</t>
+  </si>
+  <si>
     <t>Security Labels that define affected resources</t>
   </si>
   <si>
@@ -1217,6 +1296,9 @@
   </si>
   <si>
     <t>Typical use of this is a Document code with class = CDA.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>If this code is found in an instance, then the exception applies.</t>
@@ -1629,12 +1711,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN69"/>
+  <dimension ref="A1:AN75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.26953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
@@ -1669,7 +1751,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="38.8984375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="24.74609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="39.6328125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -3176,7 +3258,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>93</v>
+        <v>181</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>83</v>
@@ -3194,10 +3276,10 @@
         <v>173</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3227,23 +3309,23 @@
         <v>177</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>180</v>
@@ -3261,27 +3343,27 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>180</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>81</v>
@@ -3306,10 +3388,10 @@
         <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3321,7 +3403,7 @@
         <v>81</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>81</v>
@@ -3339,10 +3421,10 @@
         <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3375,26 +3457,28 @@
         <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="D16" t="s" s="2">
         <v>81</v>
       </c>
@@ -3415,13 +3499,13 @@
         <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>198</v>
@@ -3435,7 +3519,7 @@
         <v>81</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>81</v>
@@ -3450,13 +3534,13 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -3474,13 +3558,13 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
@@ -3489,24 +3573,24 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AN16" t="s" s="2">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="17" hidden="true">
-      <c r="A17" t="s" s="2">
-        <v>202</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3514,13 +3598,13 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>81</v>
@@ -3529,16 +3613,16 @@
         <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3588,7 +3672,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -3603,38 +3687,38 @@
         <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL17" t="s" s="2">
+    </row>
+    <row r="18" hidden="true">
+      <c r="A18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM17" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>212</v>
+        <v>81</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>81</v>
@@ -3643,16 +3727,16 @@
         <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3702,13 +3786,13 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
@@ -3717,28 +3801,28 @@
         <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3757,15 +3841,17 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -3814,7 +3900,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -3829,10 +3915,10 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>81</v>
@@ -3841,7 +3927,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>226</v>
       </c>
@@ -3850,17 +3936,17 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>81</v>
@@ -3869,17 +3955,15 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N20" t="s" s="2">
         <v>230</v>
       </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -3934,7 +4018,7 @@
         <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>81</v>
@@ -3943,16 +4027,16 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -3971,7 +4055,7 @@
         <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>81</v>
@@ -3980,7 +4064,7 @@
         <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
         <v>233</v>
@@ -3991,7 +4075,9 @@
       <c r="M21" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="N21" s="2"/>
+      <c r="N21" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4046,7 +4132,7 @@
         <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
@@ -4058,7 +4144,7 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>81</v>
+        <v>237</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
@@ -4069,10 +4155,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4083,7 +4169,7 @@
         <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>81</v>
@@ -4095,13 +4181,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4152,19 +4238,19 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
@@ -4173,7 +4259,7 @@
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4188,14 +4274,14 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4207,17 +4293,15 @@
         <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>140</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4266,19 +4350,19 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
@@ -4287,7 +4371,7 @@
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4295,14 +4379,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>246</v>
+        <v>138</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4315,26 +4399,24 @@
         <v>81</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O24" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>81</v>
       </c>
@@ -4382,7 +4464,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4403,7 +4485,7 @@
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>136</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4411,42 +4493,46 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
       </c>
@@ -4494,19 +4580,19 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>253</v>
+        <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>81</v>
@@ -4515,7 +4601,7 @@
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4523,10 +4609,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4552,14 +4638,12 @@
         <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -4608,7 +4692,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -4617,7 +4701,7 @@
         <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>105</v>
@@ -4637,10 +4721,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4660,23 +4744,21 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
       </c>
@@ -4685,7 +4767,7 @@
         <v>81</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>81</v>
@@ -4700,13 +4782,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -4724,7 +4806,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -4733,7 +4815,7 @@
         <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>105</v>
@@ -4753,10 +4835,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4767,7 +4849,7 @@
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -4779,16 +4861,20 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>233</v>
+        <v>173</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -4797,7 +4883,7 @@
         <v>81</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>81</v>
@@ -4812,13 +4898,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>81</v>
+        <v>270</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -4836,16 +4922,16 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>81</v>
+        <v>259</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>105</v>
@@ -4865,10 +4951,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4879,7 +4965,7 @@
         <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -4888,16 +4974,16 @@
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4948,19 +5034,19 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
@@ -4969,7 +5055,7 @@
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -4977,21 +5063,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5003,17 +5089,15 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>140</v>
+        <v>244</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5062,19 +5146,19 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
@@ -5083,7 +5167,7 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5091,14 +5175,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>246</v>
+        <v>138</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5111,26 +5195,24 @@
         <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O31" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5178,7 +5260,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5199,7 +5281,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>136</v>
+        <v>247</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5207,42 +5289,46 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>272</v>
+        <v>139</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5290,19 +5376,19 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
@@ -5311,7 +5397,7 @@
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5319,10 +5405,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5330,7 +5416,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
@@ -5342,16 +5428,16 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5402,10 +5488,10 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>93</v>
@@ -5431,10 +5517,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5457,13 +5543,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>203</v>
+        <v>282</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5514,7 +5600,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -5541,12 +5627,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5554,28 +5640,28 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5626,7 +5712,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -5653,12 +5739,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5666,28 +5752,28 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>238</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>239</v>
+        <v>290</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5738,7 +5824,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -5750,7 +5836,7 @@
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
@@ -5759,7 +5845,7 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -5767,21 +5853,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -5793,17 +5879,15 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>140</v>
+        <v>244</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -5852,19 +5936,19 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -5873,7 +5957,7 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -5881,14 +5965,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>246</v>
+        <v>138</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5901,26 +5985,24 @@
         <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O38" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -5968,7 +6050,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -5989,52 +6071,54 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>136</v>
+        <v>247</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I39" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6058,13 +6142,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6082,19 +6166,19 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>288</v>
+        <v>255</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6103,7 +6187,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6137,15 +6221,17 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6170,13 +6256,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -6221,12 +6307,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6234,28 +6320,28 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6306,7 +6392,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -6318,7 +6404,7 @@
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>81</v>
@@ -6327,7 +6413,7 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6335,21 +6421,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -6361,17 +6447,15 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>140</v>
+        <v>244</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6408,31 +6492,31 @@
         <v>81</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
@@ -6441,50 +6525,50 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>303</v>
+        <v>140</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>304</v>
+        <v>249</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>305</v>
+        <v>142</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6522,51 +6606,51 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>81</v>
+        <v>307</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>306</v>
+        <v>250</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AM43" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="B44" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6574,13 +6658,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>81</v>
@@ -6589,24 +6673,22 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q44" t="s" s="2">
-        <v>314</v>
-      </c>
+      <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
         <v>81</v>
       </c>
@@ -6650,7 +6732,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -6659,7 +6741,7 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
@@ -6668,10 +6750,10 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -6679,10 +6761,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6690,10 +6772,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -6702,76 +6784,80 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="R45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="R45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AC45" s="2"/>
-      <c r="AD45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>318</v>
-      </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>105</v>
@@ -6780,10 +6866,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6791,10 +6877,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6802,10 +6888,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -6817,20 +6903,22 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>238</v>
+        <v>325</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>239</v>
+        <v>326</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q46" s="2"/>
+      <c r="Q46" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="R46" t="s" s="2">
         <v>81</v>
       </c>
@@ -6862,31 +6950,29 @@
         <v>81</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
@@ -6895,7 +6981,7 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6903,21 +6989,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -6929,17 +7015,15 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>140</v>
+        <v>244</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -6988,19 +7072,19 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7009,7 +7093,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7017,14 +7101,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>246</v>
+        <v>138</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7037,26 +7121,24 @@
         <v>81</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O48" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7104,7 +7186,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7125,7 +7207,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>136</v>
+        <v>247</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7133,42 +7215,46 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7192,13 +7278,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>330</v>
+        <v>81</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7216,19 +7302,19 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>326</v>
+        <v>255</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -7237,7 +7323,7 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7245,10 +7331,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7271,7 +7357,7 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>332</v>
+        <v>173</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>333</v>
@@ -7304,13 +7390,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7328,7 +7414,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>93</v>
@@ -7355,16 +7441,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7373,10 +7457,10 @@
         <v>93</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>81</v>
@@ -7385,24 +7469,20 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q51" t="s" s="2">
-        <v>321</v>
-      </c>
+      <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7446,13 +7526,13 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
@@ -7473,26 +7553,28 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>81</v>
@@ -7501,20 +7583,24 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>238</v>
+        <v>343</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q52" s="2"/>
+      <c r="Q52" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="R52" t="s" s="2">
         <v>81</v>
       </c>
@@ -7558,19 +7644,19 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>81</v>
@@ -7579,7 +7665,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7587,21 +7673,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -7613,17 +7699,15 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>140</v>
+        <v>244</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -7672,19 +7756,19 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -7693,7 +7777,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7701,14 +7785,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>246</v>
+        <v>138</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7721,26 +7805,24 @@
         <v>81</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O54" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -7788,7 +7870,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -7809,52 +7891,54 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>136</v>
+        <v>247</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I55" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I55" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J55" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>328</v>
+        <v>254</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -7863,7 +7947,7 @@
         <v>81</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>81</v>
@@ -7878,13 +7962,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>330</v>
+        <v>81</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -7902,19 +7986,19 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>326</v>
+        <v>255</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
@@ -7923,7 +8007,7 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7931,10 +8015,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7957,7 +8041,7 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>333</v>
@@ -7965,7 +8049,9 @@
       <c r="M56" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N56" s="2"/>
+      <c r="N56" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -7975,7 +8061,7 @@
         <v>81</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>81</v>
@@ -7990,13 +8076,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8014,7 +8100,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>93</v>
@@ -8041,12 +8127,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8060,38 +8146,34 @@
         <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>173</v>
+        <v>228</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q57" t="s" s="2">
-        <v>350</v>
-      </c>
+      <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>81</v>
@@ -8106,13 +8188,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>352</v>
+        <v>81</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>353</v>
+        <v>81</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>354</v>
+        <v>81</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8130,13 +8212,13 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
@@ -8157,12 +8239,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8170,13 +8252,13 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>81</v>
@@ -8185,22 +8267,24 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>356</v>
+        <v>173</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q58" s="2"/>
+      <c r="Q58" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="R58" t="s" s="2">
         <v>81</v>
       </c>
@@ -8220,13 +8304,11 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -8244,7 +8326,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -8273,10 +8355,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8287,7 +8369,7 @@
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
@@ -8296,20 +8378,18 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>356</v>
+        <v>243</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>363</v>
+        <v>244</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -8334,13 +8414,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>367</v>
+        <v>81</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -8358,19 +8438,19 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>362</v>
+        <v>246</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -8379,7 +8459,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -8387,14 +8467,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8410,19 +8490,19 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>356</v>
+        <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>369</v>
+        <v>140</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>370</v>
+        <v>249</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>371</v>
+        <v>142</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8448,31 +8528,31 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>373</v>
+        <v>81</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>81</v>
+        <v>307</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>368</v>
+        <v>250</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -8484,7 +8564,7 @@
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>81</v>
@@ -8493,20 +8573,22 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>81</v>
       </c>
@@ -8515,29 +8597,27 @@
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>173</v>
+        <v>362</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8562,13 +8642,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>352</v>
+        <v>81</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>378</v>
+        <v>81</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>379</v>
+        <v>81</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -8586,7 +8666,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>374</v>
+        <v>250</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -8598,7 +8678,7 @@
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
@@ -8615,10 +8695,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8629,7 +8709,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -8641,18 +8721,20 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>295</v>
+        <v>366</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -8700,13 +8782,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -8718,10 +8800,10 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>81</v>
+        <v>372</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>81</v>
+        <v>373</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -8729,10 +8811,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8743,7 +8825,7 @@
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -8755,22 +8837,24 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q63" t="s" s="2">
-        <v>387</v>
-      </c>
+      <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
         <v>81</v>
       </c>
@@ -8814,13 +8898,13 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
@@ -8832,10 +8916,10 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>200</v>
+        <v>381</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -8843,10 +8927,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8857,7 +8941,7 @@
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -8866,18 +8950,20 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>237</v>
+        <v>366</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>238</v>
+        <v>383</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -8902,13 +8988,13 @@
         <v>81</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
@@ -8926,19 +9012,19 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>240</v>
+        <v>382</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -8947,7 +9033,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -8955,14 +9041,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8978,19 +9064,19 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>139</v>
+        <v>366</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>140</v>
+        <v>389</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>243</v>
+        <v>390</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>142</v>
+        <v>391</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9016,13 +9102,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9040,7 +9126,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>244</v>
+        <v>388</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -9052,7 +9138,7 @@
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>81</v>
@@ -9061,7 +9147,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9069,14 +9155,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9089,26 +9175,24 @@
         <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>139</v>
+        <v>366</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>247</v>
+        <v>395</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>248</v>
+        <v>396</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -9132,13 +9216,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>81</v>
+        <v>398</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>81</v>
+        <v>399</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9156,7 +9240,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>249</v>
+        <v>394</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -9168,7 +9252,7 @@
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -9177,7 +9261,7 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -9185,10 +9269,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9196,10 +9280,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>81</v>
@@ -9211,15 +9295,17 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -9244,13 +9330,13 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>165</v>
+        <v>404</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -9268,13 +9354,13 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
@@ -9297,10 +9383,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9308,7 +9394,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>93</v>
@@ -9323,15 +9409,17 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>397</v>
+        <v>301</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -9380,10 +9468,10 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>93</v>
@@ -9409,10 +9497,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9432,23 +9520,25 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>84</v>
+        <v>239</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q69" s="2"/>
+      <c r="Q69" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="R69" t="s" s="2">
         <v>81</v>
       </c>
@@ -9492,7 +9582,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -9513,14 +9603,692 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AN69" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN69">
+  <autoFilter ref="A1:AN75">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9530,7 +10298,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/output/StructureDefinition-pdex-provider-consent.xlsx
+++ b/output/StructureDefinition-pdex-provider-consent.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T22:49:33-04:00</t>
+    <t>2026-03-19T09:51:30-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-pdex-provider-consent.xlsx
+++ b/output/StructureDefinition-pdex-provider-consent.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:51:30-04:00</t>
+    <t>2026-03-31T21:00:10-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-pdex-provider-consent.xlsx
+++ b/output/StructureDefinition-pdex-provider-consent.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T21:00:10-04:00</t>
+    <t>2026-05-29T12:37:47-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -560,10 +560,10 @@
 </t>
   </si>
   <si>
-    <t>Which of the four areas this resource covers (extensible)</t>
-  </si>
-  <si>
-    <t>A selector of the type of consent being presented: ADR, Privacy, Treatment, Research.  This list is now extensible.</t>
+    <t>Information-disclosure scope (fixed to patient-privacy)</t>
+  </si>
+  <si>
+    <t>Fixed to `http://terminology.hl7.org/CodeSystem/consentscope#patient-privacy` ("Agreement to collect, access, use or disclose (share) information"). `Consent.scope` is structurally a "what kind of consent is this?" element bound by FHIR R4 to the [ConsentScope](http://terminology.hl7.org/CodeSystem/consentscope) code system (`treatment` / `patient-privacy` / `research` / `adr`); it is **not** a Purpose-of-Use field. The [v3 PurposeOfUse ValueSet](http://terminology.hl7.org/ValueSet/v3-PurposeOfUse) used by TEFCA applies to `Consent.provision.purpose`, not to `Consent.scope`. This profile does not redefine `provision.purpose`, so implementers retain the base R4 Consent profile's `extensible` binding to v3 PurposeOfUse on that element and may use TEFCA-style purpose codes there as appropriate.</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
